--- a/问题二/output/表3_指定日期紧急购电量.xlsx
+++ b/问题二/output/表3_指定日期紧急购电量.xlsx
@@ -427,16 +427,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
@@ -519,63 +519,51 @@
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0:00-7:20</t>
+          <t>14:10-16:20</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7152.499983333334</v>
+        <v>804.0459346659328</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0:00-6:40</t>
+          <t>6:50-7:20</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7045.338433333332</v>
+        <v>141.6298007329271</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0:00-7:00</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6690.07035</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0:00-24:00</t>
+          <t>无</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>65021.0463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10:50-11:00</t>
+          <t>16:40-17:30</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>48.65948333333313</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17:00-18:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1298.92975</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7:30-7:40</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>12.51124999999968</v>
-      </c>
+        <v>103.7765220392639</v>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
@@ -583,64 +571,86 @@
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>16:00-23:50</t>
+          <t>17:50-18:50</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11421.63741666667</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18:10-24:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>7738.015816666666</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11:00-12:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>404.9545666666681</v>
-      </c>
+        <v>602.2851526457437</v>
+      </c>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>19:10-19:20</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>696.3991125</v>
+      </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16:00-16:10</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>29.84626666666657</v>
-      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>19:40-20:00</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>145.6716666666666</v>
+      </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16:30-24:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>10783.40043333333</v>
-      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>20:10-20:50</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1199.782945589705</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>21:20-21:40</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>35.05185915401753</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/问题二/output/表3_指定日期紧急购电量.xlsx
+++ b/问题二/output/表3_指定日期紧急购电量.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
@@ -531,39 +531,39 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>141.6298007329271</v>
+        <v>185.3588218161823</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>20:20-20:40</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>319.6798315537962</v>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>16:40-17:30</t>
+          <t>16:40-17:20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>103.7765220392639</v>
+        <v>70.42631174360372</v>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20:50-21:00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>73.508906170134</v>
+      </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
@@ -571,11 +571,11 @@
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17:50-18:50</t>
+          <t>18:00-18:30</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>602.2851526457437</v>
+        <v>64.90173715036542</v>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
@@ -588,11 +588,11 @@
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>19:10-19:20</t>
+          <t>18:40-18:50</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>696.3991125</v>
+        <v>640.9183139301564</v>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
@@ -605,11 +605,11 @@
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>19:40-20:00</t>
+          <t>19:10-19:20</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>145.6716666666666</v>
+        <v>714.2555</v>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
@@ -622,11 +622,11 @@
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>20:10-20:50</t>
+          <t>19:40-20:00</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1199.782945589705</v>
+        <v>345.6086916666667</v>
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
@@ -639,11 +639,11 @@
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>21:20-21:40</t>
+          <t>20:10-20:50</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>35.05185915401753</v>
+        <v>1064.864121099245</v>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
@@ -651,6 +651,23 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>21:10-21:40</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>80.85012764282449</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
